--- a/Encollect_Web_DBS_P1/Cypress/downloads/AllocationToOwner.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/downloads/AllocationToOwner.xlsx
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>M0010811195</v>
+        <v>MMM0010811195</v>
       </c>
     </row>
   </sheetData>
